--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207024</v>
+        <v>121207062</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,47 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478180</v>
+        <v>478175</v>
       </c>
       <c r="R4" t="n">
-        <v>6851240</v>
+        <v>6851257</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -998,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207062</v>
+        <v>121207584</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,13 +1029,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478175</v>
+        <v>478074</v>
       </c>
       <c r="R5" t="n">
-        <v>6851257</v>
+        <v>6851345</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,22 +1079,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207584</v>
+        <v>121207024</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,20 +1124,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478074</v>
+        <v>478180</v>
       </c>
       <c r="R6" t="n">
-        <v>6851345</v>
+        <v>6851240</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207062</v>
+        <v>121207584</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478175</v>
+        <v>478074</v>
       </c>
       <c r="R4" t="n">
-        <v>6851257</v>
+        <v>6851345</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207584</v>
+        <v>121207062</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478074</v>
+        <v>478175</v>
       </c>
       <c r="R5" t="n">
-        <v>6851345</v>
+        <v>6851257</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1079,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207584</v>
+        <v>121207024</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,20 +920,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478074</v>
+        <v>478180</v>
       </c>
       <c r="R4" t="n">
-        <v>6851345</v>
+        <v>6851240</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +986,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207062</v>
+        <v>121207584</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478175</v>
+        <v>478074</v>
       </c>
       <c r="R5" t="n">
-        <v>6851257</v>
+        <v>6851345</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,22 +1088,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207024</v>
+        <v>121207062</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,47 +1112,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478180</v>
+        <v>478175</v>
       </c>
       <c r="R6" t="n">
-        <v>6851240</v>
+        <v>6851257</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207024</v>
+        <v>121207062</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,47 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478180</v>
+        <v>478175</v>
       </c>
       <c r="R4" t="n">
-        <v>6851240</v>
+        <v>6851257</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -998,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207584</v>
+        <v>121207024</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,20 +1022,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478074</v>
+        <v>478180</v>
       </c>
       <c r="R5" t="n">
-        <v>6851345</v>
+        <v>6851240</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,22 +1088,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207062</v>
+        <v>121207584</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478175</v>
+        <v>478074</v>
       </c>
       <c r="R6" t="n">
-        <v>6851257</v>
+        <v>6851345</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207062</v>
+        <v>121207024</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478175</v>
+        <v>478180</v>
       </c>
       <c r="R4" t="n">
-        <v>6851257</v>
+        <v>6851240</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207024</v>
+        <v>121207062</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,47 +1010,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478180</v>
+        <v>478175</v>
       </c>
       <c r="R5" t="n">
-        <v>6851240</v>
+        <v>6851257</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1103,7 +1103,7 @@
         <v>121207584</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207024</v>
+        <v>121207584</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -920,29 +920,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478180</v>
+        <v>478074</v>
       </c>
       <c r="R4" t="n">
-        <v>6851240</v>
+        <v>6851345</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207062</v>
+        <v>121207024</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,38 +1001,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478175</v>
+        <v>478180</v>
       </c>
       <c r="R5" t="n">
-        <v>6851257</v>
+        <v>6851240</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207584</v>
+        <v>121207062</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,25 +1112,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478074</v>
+        <v>478175</v>
       </c>
       <c r="R6" t="n">
-        <v>6851345</v>
+        <v>6851257</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207584</v>
+        <v>121207062</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478074</v>
+        <v>478175</v>
       </c>
       <c r="R4" t="n">
-        <v>6851345</v>
+        <v>6851257</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207024</v>
+        <v>121207584</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,29 +1022,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478180</v>
+        <v>478074</v>
       </c>
       <c r="R5" t="n">
-        <v>6851240</v>
+        <v>6851345</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,22 +1079,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207062</v>
+        <v>121207024</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,38 +1103,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478175</v>
+        <v>478180</v>
       </c>
       <c r="R6" t="n">
-        <v>6851257</v>
+        <v>6851240</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207062</v>
+        <v>121207024</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478175</v>
+        <v>478180</v>
       </c>
       <c r="R4" t="n">
-        <v>6851257</v>
+        <v>6851240</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -992,7 +1001,7 @@
         <v>121207584</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121207024</v>
+        <v>121207062</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,47 +1112,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478180</v>
+        <v>478175</v>
       </c>
       <c r="R6" t="n">
-        <v>6851240</v>
+        <v>6851257</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>

--- a/artfynd/A 42706-2024 artfynd.xlsx
+++ b/artfynd/A 42706-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121207024</v>
+        <v>121207584</v>
       </c>
       <c r="B4" t="n">
         <v>98105</v>
@@ -920,29 +920,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478180</v>
+        <v>478074</v>
       </c>
       <c r="R4" t="n">
-        <v>6851240</v>
+        <v>6851345</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,19 +977,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121207584</v>
+        <v>121207024</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1031,20 +1022,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Blästerbäcken, Blästerbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478074</v>
+        <v>478180</v>
       </c>
       <c r="R5" t="n">
-        <v>6851345</v>
+        <v>6851240</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,12 +1088,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
